--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99379</v>
+        <v>99382</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99382</v>
+        <v>99383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99383</v>
+        <v>99388</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99388</v>
+        <v>99390</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99390</v>
+        <v>99396</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99396</v>
+        <v>99398</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 46978-2023 artfynd.xlsx
+++ b/artfynd/A 46978-2023 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136438742</v>
       </c>
       <c r="B2" t="n">
-        <v>99398</v>
+        <v>99399</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
